--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="22188" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8155" uniqueCount="4680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8154" uniqueCount="4680">
   <si>
     <t>date</t>
   </si>
@@ -3315,7 +3315,7 @@
     <t>01/01/2020</t>
   </si>
   <si>
-    <t>8,10,23,26,37,38</t>
+    <t>8,23,26,37,10,38</t>
   </si>
   <si>
     <t>03/01/2020</t>
@@ -21394,12 +21394,10 @@
       <c r="A542" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="B542" s="2" t="s">
+      <c r="B542" t="s">
         <v>1088</v>
       </c>
-      <c r="C542" t="s">
-        <v>6</v>
-      </c>
+      <c r="C542"/>
       <c r="D542">
         <v>539</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8280"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8147" uniqueCount="4687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8148" uniqueCount="4687">
   <si>
     <t>date</t>
   </si>
@@ -32559,10 +32559,11 @@
         <v>2989</v>
       </c>
       <c r="B1505" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1505" s="3"/>
+      <c r="J1505" t="s">
         <v>2990</v>
-      </c>
-      <c r="D1505" s="3">
-        <v>1478</v>
       </c>
       <c r="M1505" s="3"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8148" uniqueCount="4687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8147" uniqueCount="4687">
   <si>
     <t>date</t>
   </si>
@@ -32559,11 +32559,10 @@
         <v>2989</v>
       </c>
       <c r="B1505" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1505" s="3"/>
-      <c r="J1505" t="s">
         <v>2990</v>
+      </c>
+      <c r="D1505" s="3">
+        <v>1478</v>
       </c>
       <c r="M1505" s="3"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\confidential\new life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A759292-96C8-490C-9DE8-3A5B12F3226A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021319BA-4169-43B5-9303-0AC11179D079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8143" uniqueCount="4691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8141" uniqueCount="4693">
   <si>
     <t>date</t>
   </si>
@@ -14128,6 +14128,12 @@
   </si>
   <si>
     <t>19,16,44,18,28,31</t>
+  </si>
+  <si>
+    <t>11,22,20,31,33,12</t>
+  </si>
+  <si>
+    <t>26,7,42,4,11,44</t>
   </si>
 </sst>
 </file>
@@ -31542,10 +31548,10 @@
         <v>2998</v>
       </c>
       <c r="B1510" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1510" t="s">
-        <v>173</v>
+        <v>4691</v>
+      </c>
+      <c r="D1510">
+        <v>1483</v>
       </c>
     </row>
     <row r="1511" spans="1:4">
@@ -31553,10 +31559,10 @@
         <v>2999</v>
       </c>
       <c r="B1511" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1511" t="s">
-        <v>173</v>
+        <v>4692</v>
+      </c>
+      <c r="D1511">
+        <v>1484</v>
       </c>
     </row>
     <row r="1512" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\confidential\new life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021319BA-4169-43B5-9303-0AC11179D079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E68D24-3372-40B5-B08B-AC0BD8DDE413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8141" uniqueCount="4693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8140" uniqueCount="4694">
   <si>
     <t>date</t>
   </si>
@@ -14134,13 +14134,16 @@
   </si>
   <si>
     <t>26,7,42,4,11,44</t>
+  </si>
+  <si>
+    <t>33,44,14,20,35,36</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14153,6 +14156,13 @@
       <color rgb="FF0A0A0A"/>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -14217,7 +14227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -14229,6 +14239,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -31569,11 +31580,11 @@
       <c r="A1512" t="s">
         <v>3000</v>
       </c>
-      <c r="B1512" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1512" t="s">
-        <v>173</v>
+      <c r="B1512" s="11" t="s">
+        <v>4693</v>
+      </c>
+      <c r="D1512">
+        <v>1485</v>
       </c>
     </row>
     <row r="1513" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\confidential\new life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E68D24-3372-40B5-B08B-AC0BD8DDE413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D88F4B-8EFB-404A-B21C-AA78E0723059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8140" uniqueCount="4694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8139" uniqueCount="4695">
   <si>
     <t>date</t>
   </si>
@@ -14137,6 +14137,9 @@
   </si>
   <si>
     <t>33,44,14,20,35,36</t>
+  </si>
+  <si>
+    <t>43,23,11,8,38,22</t>
   </si>
 </sst>
 </file>
@@ -31591,11 +31594,11 @@
       <c r="A1513" t="s">
         <v>3001</v>
       </c>
-      <c r="B1513" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1513" t="s">
-        <v>173</v>
+      <c r="B1513" s="11" t="s">
+        <v>4694</v>
+      </c>
+      <c r="D1513">
+        <v>1486</v>
       </c>
     </row>
     <row r="1514" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\confidential\new life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D88F4B-8EFB-404A-B21C-AA78E0723059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C85EDE6-76D3-45F1-9245-4DC320DBCC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8139" uniqueCount="4695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8138" uniqueCount="4696">
   <si>
     <t>date</t>
   </si>
@@ -14140,6 +14140,9 @@
   </si>
   <si>
     <t>43,23,11,8,38,22</t>
+  </si>
+  <si>
+    <t>36,22,31,26,10,5</t>
   </si>
 </sst>
 </file>
@@ -31606,10 +31609,10 @@
         <v>3002</v>
       </c>
       <c r="B1514" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1514" t="s">
-        <v>173</v>
+        <v>4695</v>
+      </c>
+      <c r="D1514">
+        <v>1487</v>
       </c>
     </row>
     <row r="1515" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\confidential\new life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C85EDE6-76D3-45F1-9245-4DC320DBCC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70177350-D312-4A60-BE52-7ADC03FE5480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8138" uniqueCount="4696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8137" uniqueCount="4697">
   <si>
     <t>date</t>
   </si>
@@ -14143,6 +14143,9 @@
   </si>
   <si>
     <t>36,22,31,26,10,5</t>
+  </si>
+  <si>
+    <t>16,29,35,36,22,24</t>
   </si>
 </sst>
 </file>
@@ -31619,11 +31622,11 @@
       <c r="A1515" t="s">
         <v>3003</v>
       </c>
-      <c r="B1515" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1515" t="s">
-        <v>173</v>
+      <c r="B1515" s="11" t="s">
+        <v>4696</v>
+      </c>
+      <c r="D1515">
+        <v>1488</v>
       </c>
     </row>
     <row r="1516" spans="1:4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\OneDrive\Desktop\confidential\new life\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70177350-D312-4A60-BE52-7ADC03FE5480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7F0994-AE7A-4013-AEAA-C1B3E4ED53A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8137" uniqueCount="4697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8134" uniqueCount="4700">
   <si>
     <t>date</t>
   </si>
@@ -14146,6 +14146,15 @@
   </si>
   <si>
     <t>16,29,35,36,22,24</t>
+  </si>
+  <si>
+    <t>34,36,44,37,6,30</t>
+  </si>
+  <si>
+    <t>30,5,45,8,18,37</t>
+  </si>
+  <si>
+    <t>5,38,7,13,45,19</t>
   </si>
 </sst>
 </file>
@@ -31633,33 +31642,33 @@
       <c r="A1516" t="s">
         <v>3004</v>
       </c>
-      <c r="B1516" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1516" t="s">
-        <v>173</v>
+      <c r="B1516" s="11" t="s">
+        <v>4699</v>
+      </c>
+      <c r="D1516">
+        <v>1489</v>
       </c>
     </row>
     <row r="1517" spans="1:4">
       <c r="A1517" t="s">
         <v>3005</v>
       </c>
-      <c r="B1517" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1517" t="s">
-        <v>173</v>
+      <c r="B1517" s="11" t="s">
+        <v>4698</v>
+      </c>
+      <c r="D1517">
+        <v>1490</v>
       </c>
     </row>
     <row r="1518" spans="1:4">
       <c r="A1518" t="s">
         <v>3006</v>
       </c>
-      <c r="B1518" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1518" t="s">
-        <v>173</v>
+      <c r="B1518" s="11" t="s">
+        <v>4697</v>
+      </c>
+      <c r="D1518">
+        <v>1491</v>
       </c>
     </row>
     <row r="1519" spans="1:4">
